--- a/assets/template/product_template.xlsx
+++ b/assets/template/product_template.xlsx
@@ -1,31 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Test-Team\Desktop\TMax协议\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69064CA1-D6D3-40EA-AA26-FB76F043DDE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2680" yWindow="1500" windowWidth="28240" windowHeight="17440" xr2:uid="{752BAC88-3D22-6345-9E5D-6A586CA68B77}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>ProductNumber</t>
   </si>
@@ -57,42 +46,62 @@
     <t>LimitLow</t>
   </si>
   <si>
-    <t>一个菜单的名称</t>
-  </si>
-  <si>
-    <t>Тестовый True Тестовый True</t>
-  </si>
-  <si>
-    <t>西红柿鸡蛋</t>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>Mela</t>
+  </si>
+  <si>
+    <t>Apfel</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+    </font>
+    <font>
       <b/>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -104,8 +113,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF9CC2E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -119,103 +127,77 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -235,7 +217,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CEEACA"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -273,7 +255,7 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -303,12 +285,29 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -338,6 +337,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -489,155 +505,157 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F1E1092-59D6-0841-9542-AE5505D0AA25}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.002500000000003" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.8330078125" customWidth="1" style="13"/>
+    <col min="2" max="2" width="13.998046875" customWidth="1" style="5"/>
+    <col min="3" max="3" width="9.6650390625" customWidth="1" style="12"/>
+    <col min="4" max="4" width="10.3330078125" customWidth="1" style="12"/>
+    <col min="5" max="5" width="9" customWidth="1" style="12"/>
+    <col min="6" max="6" width="6.9990234375" customWidth="1" style="6"/>
+    <col min="7" max="7" width="11.33203125" customWidth="1" style="12"/>
+    <col min="8" max="8" width="8.4990234375" customWidth="1" style="12"/>
+    <col min="9" max="9" width="10.5" customWidth="1" style="12"/>
+    <col min="10" max="10" width="9.3310546875" customWidth="1" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" ht="14.002500000000003" customHeight="1">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2">
-        <v>1</v>
-      </c>
-      <c r="F2" s="3">
+      <c r="C2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="14.002500000000003" customHeight="1">
+      <c r="A3" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0.5</v>
+      <c r="B3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3">
-        <v>22.22</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="J3" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+    <row r="4" ht="14.002500000000003" customHeight="1">
+      <c r="A4" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1</v>
-      </c>
-      <c r="F4" s="3">
-        <v>33.33</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0.5</v>
+      <c r="C4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576" xr:uid="{ECDA90DA-B366-4D81-BE4E-86AE0F6D61AB}">
-      <formula1>0</formula1>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2 F3 F4 F5 F6:F1048576">
       <formula2>10000000</formula2>
     </dataValidation>
   </dataValidations>

--- a/assets/template/product_template.xlsx
+++ b/assets/template/product_template.xlsx
@@ -1,31 +1,119 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="2680" yWindow="1500" windowWidth="28240" windowHeight="17440" xr2:uid="{752BAC88-3D22-6345-9E5D-6A586CA68B77}"/>
+    <workbookView windowWidth="24045" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Instructions" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <si>
-    <t>ProductNumber</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="29">
+  <si>
+    <t>PLU</t>
+  </si>
+  <si>
+    <t>Product Code</t>
+  </si>
+  <si>
+    <t>Item Code</t>
   </si>
   <si>
     <t>ProductName</t>
   </si>
   <si>
-    <t>PriceUnit</t>
-  </si>
-  <si>
-    <t>TaxModel</t>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>UnitWeight</t>
+  </si>
+  <si>
+    <t>PreTare</t>
+  </si>
+  <si>
+    <t>LimitHigh</t>
+  </si>
+  <si>
+    <t>LimitLow</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>Mela</t>
+  </si>
+  <si>
+    <t>Apfel</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1.Please select header 1 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>↑</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> or header 2 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>↓</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>according to the scale type.
+2.Click on the right to view the filling instructions.  
+3.Delete this row and other templates in this Sheet page when issuing.</t>
+    </r>
+  </si>
+  <si>
+    <t>Click me: View descriptions.</t>
   </si>
   <si>
     <t>TaxType</t>
@@ -34,44 +122,338 @@
     <t>Price</t>
   </si>
   <si>
-    <t>UnitWeight</t>
-  </si>
-  <si>
-    <t>PreTare</t>
-  </si>
-  <si>
-    <t>LimitHigh</t>
-  </si>
-  <si>
-    <t>LimitLow</t>
-  </si>
-  <si>
-    <t>Apple</t>
-  </si>
-  <si>
-    <t>Mela</t>
-  </si>
-  <si>
-    <t>Apfel</t>
+    <t>Instructions</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Select this header for the weighing scale. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>↓</t>
+    </r>
+  </si>
+  <si>
+    <t>1-9999</t>
+  </si>
+  <si>
+    <t>Not in use yet</t>
+  </si>
+  <si>
+    <t>The length is 30. Characters need scale support for display and only printer support for printing.</t>
+  </si>
+  <si>
+    <r>
+      <t>0-g</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1-kg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2-lb</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3-oz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4-lboz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5-tj</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>6-gj</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7-t</t>
+    </r>
+  </si>
+  <si>
+    <t>Unit: g</t>
+  </si>
+  <si>
+    <t>Unit: Kg</t>
+  </si>
+  <si>
+    <t>With unit weight, upper &amp; lower limit units are pcs and must be integers; without, they are the same as Unit.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Select this header for the price scale. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ↓ </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>0-kg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1-100g</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2-pcs</t>
+    </r>
+  </si>
+  <si>
+    <t>0-tax1
+1-tax2
+2-tax3</t>
+  </si>
+  <si>
+    <t>unit Price</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="34">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
+      <b/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="20"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -80,31 +462,181 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -114,10 +646,197 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF9CC2E5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -127,83 +846,501 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -217,7 +1354,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CEEACA"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -252,7 +1389,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -285,26 +1422,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -337,23 +1457,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -495,170 +1598,447 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F1E1092-59D6-0841-9542-AE5505D0AA25}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.002500000000003" customHeight="1"/>
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="14.8330078125" customWidth="1" style="13"/>
-    <col min="2" max="2" width="13.998046875" customWidth="1" style="5"/>
-    <col min="3" max="3" width="9.6650390625" customWidth="1" style="12"/>
-    <col min="4" max="4" width="10.3330078125" customWidth="1" style="12"/>
-    <col min="5" max="5" width="9" customWidth="1" style="12"/>
-    <col min="6" max="6" width="6.9990234375" customWidth="1" style="6"/>
-    <col min="7" max="7" width="11.33203125" customWidth="1" style="12"/>
-    <col min="8" max="8" width="8.4990234375" customWidth="1" style="12"/>
-    <col min="9" max="9" width="10.5" customWidth="1" style="12"/>
-    <col min="10" max="10" width="9.3310546875" customWidth="1" style="12"/>
+    <col min="1" max="1" width="9.5" style="9" customWidth="1"/>
+    <col min="2" max="2" width="14.5" style="9" customWidth="1"/>
+    <col min="3" max="3" width="11.125" style="9" customWidth="1"/>
+    <col min="4" max="4" width="19.75" style="10" customWidth="1"/>
+    <col min="5" max="5" width="13.25" style="11" customWidth="1"/>
+    <col min="6" max="7" width="14" style="11" customWidth="1"/>
+    <col min="8" max="8" width="14" style="12" customWidth="1"/>
+    <col min="9" max="9" width="14" style="11" customWidth="1"/>
+    <col min="10" max="10" width="10.25" style="11" customWidth="1"/>
+    <col min="11" max="11" width="10.375" style="11" customWidth="1"/>
+    <col min="12" max="12" width="9.625" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.002500000000003" customHeight="1">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
+    <row r="1" customHeight="1" spans="1:12">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1"/>
+      <c r="L1"/>
+    </row>
+    <row r="2" customHeight="1" spans="1:12">
+      <c r="A2" s="13">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="14" t="s">
         <v>9</v>
       </c>
+      <c r="E2" s="13">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="6">
+        <v>0</v>
+      </c>
+      <c r="I2" s="6">
+        <v>0</v>
+      </c>
+      <c r="K2"/>
+      <c r="L2"/>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="8" t="n">
+    <row r="3" customHeight="1" spans="1:12">
+      <c r="A3" s="13">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="13">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0</v>
+      </c>
+      <c r="K3"/>
+      <c r="L3"/>
+    </row>
+    <row r="4" customHeight="1" spans="1:12">
+      <c r="A4" s="15">
+        <v>3</v>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="15">
+        <v>0</v>
+      </c>
+      <c r="F4" s="16">
+        <v>0</v>
+      </c>
+      <c r="G4" s="16">
+        <v>0</v>
+      </c>
+      <c r="H4" s="18">
+        <v>0</v>
+      </c>
+      <c r="I4" s="18">
+        <v>0</v>
+      </c>
+      <c r="K4"/>
+      <c r="L4"/>
+    </row>
+    <row r="5" ht="76" customHeight="1" spans="1:12">
+      <c r="A5" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="29"/>
+      <c r="K5"/>
+      <c r="L5"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:12">
+      <c r="A6" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C6" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6"/>
+      <c r="K6"/>
+      <c r="L6"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:12">
+      <c r="A7" s="25">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="25">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+      <c r="G7" s="27">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0</v>
+      </c>
+      <c r="I7"/>
+      <c r="K7"/>
+      <c r="L7"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:8">
+      <c r="A8" s="25">
+        <v>2</v>
+      </c>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="8" t="n">
+      <c r="E8" s="25">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0</v>
+      </c>
+      <c r="G8" s="27">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="14.002500000000003" customHeight="1">
-      <c r="A3" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="9" t="s">
+    <row r="9" customHeight="1" spans="1:8">
+      <c r="A9" s="25">
+        <v>3</v>
+      </c>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="14.002500000000003" customHeight="1">
-      <c r="A4" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="8" t="n">
+      <c r="E9" s="25">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0</v>
+      </c>
+      <c r="G9" s="27">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="F5:I5"/>
+  </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2 F3 F4 F5 F6:F1048576">
-      <formula2>10000000</formula2>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7:G9 H10:H1048576">
+      <formula1>10000000</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="F5:I5" location="Instructions!A1" display="Click me: View descriptions."/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelRow="6"/>
+  <cols>
+    <col min="1" max="1" width="8.375" customWidth="1"/>
+    <col min="2" max="2" width="14.5" customWidth="1"/>
+    <col min="3" max="3" width="12.875" customWidth="1"/>
+    <col min="4" max="4" width="41.625" customWidth="1"/>
+    <col min="5" max="5" width="6.75" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="8.75" customWidth="1"/>
+    <col min="8" max="9" width="17.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27.75" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" ht="29" customHeight="1" spans="1:9">
+      <c r="A2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="114" spans="1:9">
+      <c r="A4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" ht="33" customHeight="1" spans="1:9">
+      <c r="A5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" ht="42.75" spans="1:8">
+      <c r="A7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A5:I5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>